--- a/Config/Datas/Tables/z_战斗界面_CombatUiSetConfig.xlsx
+++ b/Config/Datas/Tables/z_战斗界面_CombatUiSetConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCombatUiSet" sheetId="1" r:id="Rbc7bc5425b7c47db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbCombatUiSet" sheetId="1" r:id="R286c19d1f27449c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -598,6 +598,21 @@
       <x:c r="U1" s="48" t="str">
         <x:v>rankFormat</x:v>
       </x:c>
+      <x:c r="V1" t="str">
+        <x:v>chestPanelPrefabResourceId</x:v>
+      </x:c>
+      <x:c r="W1" t="str">
+        <x:v>eventHudPrefabResourceId</x:v>
+      </x:c>
+      <x:c r="X1" t="str">
+        <x:v>eliteStatusFormat</x:v>
+      </x:c>
+      <x:c r="Y1" t="str">
+        <x:v>evolutionReadyFormat</x:v>
+      </x:c>
+      <x:c r="Z1" t="str">
+        <x:v>chestStatusFormat</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="9" t="str">
@@ -661,6 +676,21 @@
         <x:v>string</x:v>
       </x:c>
       <x:c r="U2" s="54" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="V2" t="str">
+        <x:v>int#ref=TbResource</x:v>
+      </x:c>
+      <x:c r="W2" t="str">
+        <x:v>int#ref=TbResource</x:v>
+      </x:c>
+      <x:c r="X2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="Y2" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="Z2" t="str">
         <x:v>string</x:v>
       </x:c>
     </x:row>
@@ -688,6 +718,11 @@
       <x:c r="S3" s="60"/>
       <x:c r="T3" s="60"/>
       <x:c r="U3" s="60"/>
+      <x:c r="V3"/>
+      <x:c r="W3"/>
+      <x:c r="X3"/>
+      <x:c r="Y3"/>
+      <x:c r="Z3"/>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="13" t="str">
@@ -752,6 +787,21 @@
       </x:c>
       <x:c r="U4" s="66" t="str">
         <x:v>升级卡等级格式</x:v>
+      </x:c>
+      <x:c r="V4" t="str">
+        <x:v>宝箱奖励面板</x:v>
+      </x:c>
+      <x:c r="W4" t="str">
+        <x:v>事件状态HUD</x:v>
+      </x:c>
+      <x:c r="X4" t="str">
+        <x:v>精英名称及相对距离</x:v>
+      </x:c>
+      <x:c r="Y4" t="str">
+        <x:v>可进化状态</x:v>
+      </x:c>
+      <x:c r="Z4" t="str">
+        <x:v>场上未领取箱数</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -816,6 +866,21 @@
       <x:c r="U5" s="42" t="str">
         <x:v>等级 {0}/{1}</x:v>
       </x:c>
+      <x:c r="V5" t="n">
+        <x:v>960009</x:v>
+      </x:c>
+      <x:c r="W5" t="n">
+        <x:v>960010</x:v>
+      </x:c>
+      <x:c r="X5" t="str">
+        <x:v>精英：{0}　距离 {1:0.0}</x:v>
+      </x:c>
+      <x:c r="Y5" t="str">
+        <x:v>可进化 {0} 把：靠近宝箱觉醒</x:v>
+      </x:c>
+      <x:c r="Z5" t="str">
+        <x:v>场上宝箱 {0}</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
